--- a/config_Keith.xlsx
+++ b/config_Keith.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/keithtan_2022_accountancy_smu_edu_sg/Documents/Desktop/smu/subject/y4s2/capstone/ETL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{8A2B9805-7A9B-204D-912C-31490BC44652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A9C2365-A982-42C1-84B1-AED24BE9790F}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{8A2B9805-7A9B-204D-912C-31490BC44652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26C93629-64EB-4BE0-8481-B0D905757549}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="paths" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>raw_data</t>
   </si>
@@ -71,6 +71,18 @@
   </si>
   <si>
     <t>C:\Users\user\OneDrive - Singapore Management University\Desktop\smu\subject\y4s2\capstone\schemas.xlsx</t>
+  </si>
+  <si>
+    <t>combined_data</t>
+  </si>
+  <si>
+    <t>C:\Users\user\OneDrive - Singapore Management University\Desktop\smu\subject\y4s2\capstone\combined data</t>
+  </si>
+  <si>
+    <t>shop_mapping</t>
+  </si>
+  <si>
+    <t>C:\Users\user\OneDrive - Singapore Management University\Desktop\smu\subject\y4s2\capstone\shop_mapping.xlsx</t>
   </si>
 </sst>
 </file>
@@ -123,6 +135,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -388,13 +404,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -402,7 +418,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -410,7 +426,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -418,12 +434,28 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -434,14 +466,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9EF9E44-D244-4891-A14F-02851A432852}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.1796875" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -452,7 +484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -463,7 +495,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -474,7 +506,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
